--- a/AAII_Financials/Yearly/MRVSY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MRVSY_YR_FIN.xlsx
@@ -894,10 +894,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E14" s="3">
-        <v>5400</v>
+        <v>6400</v>
       </c>
       <c r="F14" s="3">
         <v>3200</v>
@@ -972,10 +972,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9255600</v>
+        <v>9255100</v>
       </c>
       <c r="E17" s="3">
-        <v>5110400</v>
+        <v>5109500</v>
       </c>
       <c r="F17" s="3">
         <v>5116300</v>
@@ -1005,10 +1005,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>699100</v>
+        <v>699500</v>
       </c>
       <c r="E18" s="3">
-        <v>398000</v>
+        <v>398900</v>
       </c>
       <c r="F18" s="3">
         <v>425700</v>
@@ -1053,7 +1053,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>114800</v>
+        <v>115200</v>
       </c>
       <c r="E20" s="3">
         <v>301400</v>
@@ -1086,10 +1086,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>753200</v>
+        <v>753400</v>
       </c>
       <c r="E21" s="3">
-        <v>204700</v>
+        <v>205600</v>
       </c>
       <c r="F21" s="3">
         <v>433500</v>
@@ -1449,7 +1449,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-114800</v>
+        <v>-115200</v>
       </c>
       <c r="E32" s="3">
         <v>-301400</v>
@@ -2621,7 +2621,7 @@
         <v>112400</v>
       </c>
       <c r="E72" s="3">
-        <v>-90100</v>
+        <v>-93300</v>
       </c>
       <c r="F72" s="3">
         <v>201900</v>
@@ -3100,7 +3100,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>859900</v>
+        <v>853800</v>
       </c>
       <c r="E89" s="3">
         <v>1060100</v>
@@ -3247,7 +3247,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-224400</v>
+        <v>-218400</v>
       </c>
       <c r="E94" s="3">
         <v>-1045400</v>
